--- a/results/auto_Cape_Town_Women_and_Family_Support.xlsx
+++ b/results/auto_Cape_Town_Women_and_Family_Support.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -113,9 +113,6 @@
   </si>
   <si>
     <t>info@wlce.co.za</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -486,9 +483,6 @@
       <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
@@ -503,9 +497,6 @@
       <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -520,9 +511,6 @@
       <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
@@ -537,9 +525,6 @@
       <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -554,9 +539,6 @@
       <c r="D6" t="s">
         <v>26</v>
       </c>
-      <c r="G6" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
@@ -571,9 +553,6 @@
       <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="G7" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
@@ -588,9 +567,6 @@
       <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="G8" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
@@ -605,9 +581,6 @@
       <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="G9" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
@@ -622,9 +595,6 @@
       <c r="D10" t="s">
         <v>30</v>
       </c>
-      <c r="G10" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -638,9 +608,6 @@
       </c>
       <c r="D11" t="s">
         <v>26</v>
-      </c>
-      <c r="G11" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7">

--- a/results/auto_Cape_Town_Women_and_Family_Support.xlsx
+++ b/results/auto_Cape_Town_Women_and_Family_Support.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>info@wlce.co.za</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -483,6 +486,9 @@
       <c r="D2" t="s">
         <v>22</v>
       </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
@@ -497,6 +503,9 @@
       <c r="D3" t="s">
         <v>23</v>
       </c>
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -511,6 +520,9 @@
       <c r="D4" t="s">
         <v>24</v>
       </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
@@ -525,6 +537,9 @@
       <c r="D5" t="s">
         <v>25</v>
       </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -539,6 +554,9 @@
       <c r="D6" t="s">
         <v>26</v>
       </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
@@ -553,6 +571,9 @@
       <c r="D7" t="s">
         <v>27</v>
       </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
@@ -567,6 +588,9 @@
       <c r="D8" t="s">
         <v>28</v>
       </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
@@ -581,6 +605,9 @@
       <c r="D9" t="s">
         <v>29</v>
       </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
@@ -595,6 +622,9 @@
       <c r="D10" t="s">
         <v>30</v>
       </c>
+      <c r="G10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -609,6 +639,9 @@
       <c r="D11" t="s">
         <v>26</v>
       </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
@@ -623,6 +656,9 @@
       <c r="D12" t="s">
         <v>31</v>
       </c>
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
@@ -637,6 +673,9 @@
       <c r="D13" t="s">
         <v>32</v>
       </c>
+      <c r="G13" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
@@ -650,6 +689,9 @@
       </c>
       <c r="D14" t="s">
         <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
